--- a/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.04629999999999999</v>
+        <v>0.03655</v>
       </c>
       <c r="E2">
-        <v>0.08865000000000001</v>
+        <v>0.059</v>
       </c>
       <c r="F2">
-        <v>0.201</v>
+        <v>0.0999</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001094304645108403</v>
+        <v>-8.166208091688492e-05</v>
       </c>
       <c r="J2">
-        <v>-9.477474406800798e-05</v>
+        <v>-6.756730813059875e-05</v>
       </c>
       <c r="K2">
-        <v>4280.2</v>
+        <v>5764.6</v>
       </c>
       <c r="L2">
-        <v>0.2520477926238244</v>
+        <v>0.3367153229245157</v>
       </c>
       <c r="M2">
-        <v>745.59</v>
+        <v>1713.187</v>
       </c>
       <c r="N2">
-        <v>0.01865509381466256</v>
+        <v>0.06030925802715556</v>
       </c>
       <c r="O2">
-        <v>0.1741951310686417</v>
+        <v>0.2971909586094438</v>
       </c>
       <c r="P2">
-        <v>732.21</v>
+        <v>1225.69</v>
       </c>
       <c r="Q2">
-        <v>0.01832031846193494</v>
+        <v>0.04314791932889071</v>
       </c>
       <c r="R2">
-        <v>0.1710691089201439</v>
+        <v>0.212623599208965</v>
       </c>
       <c r="S2">
-        <v>13.38</v>
+        <v>487.4970000000001</v>
       </c>
       <c r="T2">
-        <v>0.01794551965557478</v>
+        <v>0.2845556264435815</v>
       </c>
       <c r="U2">
-        <v>63556.1</v>
+        <v>8962.799999999999</v>
       </c>
       <c r="V2">
-        <v>1.590210448093557</v>
+        <v>0.3155171139203075</v>
       </c>
       <c r="W2">
-        <v>0.07778250389905006</v>
+        <v>0.05842793343817335</v>
       </c>
       <c r="X2">
-        <v>0.09441147955364586</v>
+        <v>0.1330762479018652</v>
       </c>
       <c r="Y2">
-        <v>-0.0166289756545958</v>
+        <v>-0.07464831446369183</v>
       </c>
       <c r="Z2">
-        <v>0.2005034362162944</v>
+        <v>0.162349586393769</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04104811182897827</v>
+        <v>0.0646698417387141</v>
       </c>
       <c r="AC2">
-        <v>-0.04104811182897827</v>
+        <v>-0.06468176975758438</v>
       </c>
       <c r="AD2">
-        <v>117058.9</v>
+        <v>89794.39999999999</v>
       </c>
       <c r="AE2">
-        <v>12.29657659591869</v>
+        <v>9.770314957525807</v>
       </c>
       <c r="AF2">
-        <v>117071.1965765959</v>
+        <v>89804.17031495753</v>
       </c>
       <c r="AG2">
-        <v>53515.09657659592</v>
+        <v>80841.37031495753</v>
       </c>
       <c r="AH2">
-        <v>0.7454945648846495</v>
+        <v>0.7596946886160805</v>
       </c>
       <c r="AI2">
-        <v>0.6643340149541985</v>
+        <v>0.6308064254996384</v>
       </c>
       <c r="AJ2">
-        <v>0.5724629772980098</v>
+        <v>0.7399798466178423</v>
       </c>
       <c r="AK2">
-        <v>0.4749834086967208</v>
+        <v>0.6060015030148722</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>194773.544093178</v>
+        <v>161500.7194244604</v>
       </c>
       <c r="AP2">
-        <v>89043.42192445244</v>
+        <v>145398.1480484848</v>
       </c>
     </row>
     <row r="3">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09029999999999999</v>
+        <v>0.045</v>
       </c>
       <c r="E3">
-        <v>0.172</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,85 +737,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>119.2</v>
+        <v>78.2</v>
       </c>
       <c r="L3">
-        <v>0.4162011173184358</v>
+        <v>0.3466312056737589</v>
       </c>
       <c r="M3">
-        <v>14.36</v>
+        <v>14.597</v>
       </c>
       <c r="N3">
-        <v>0.01962821213778021</v>
+        <v>0.0231441255747582</v>
       </c>
       <c r="O3">
-        <v>0.1204697986577181</v>
+        <v>0.1866624040920716</v>
       </c>
       <c r="P3">
-        <v>9.789999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="Q3">
-        <v>0.01338162930563149</v>
+        <v>0.02267322023148882</v>
       </c>
       <c r="R3">
-        <v>0.08213087248322147</v>
+        <v>0.1828644501278772</v>
       </c>
       <c r="S3">
-        <v>4.57</v>
+        <v>0.2970000000000006</v>
       </c>
       <c r="T3">
-        <v>0.3182451253481894</v>
+        <v>0.0203466465712133</v>
       </c>
       <c r="U3">
-        <v>103.7</v>
+        <v>146.6</v>
       </c>
       <c r="V3">
-        <v>0.1417441224712958</v>
+        <v>0.2324401458696686</v>
       </c>
       <c r="W3">
-        <v>0.07656731757451182</v>
+        <v>0.04674237895995218</v>
       </c>
       <c r="X3">
-        <v>0.09441147955364586</v>
+        <v>0.1392123704045994</v>
       </c>
       <c r="Y3">
-        <v>-0.01784416197913404</v>
+        <v>-0.09246999144464726</v>
       </c>
       <c r="Z3">
-        <v>0.0794628488985073</v>
+        <v>0.06251212280750366</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03992583766662627</v>
+        <v>0.06338066233987308</v>
       </c>
       <c r="AC3">
-        <v>-0.03992583766662627</v>
+        <v>-0.06338066233987308</v>
       </c>
       <c r="AD3">
-        <v>2004.8</v>
+        <v>2016.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2004.8</v>
+        <v>2016.6</v>
       </c>
       <c r="AG3">
-        <v>1901.1</v>
+        <v>1870</v>
       </c>
       <c r="AH3">
-        <v>0.732641426692004</v>
+        <v>0.7617572621161183</v>
       </c>
       <c r="AI3">
-        <v>0.5451974328293266</v>
+        <v>0.5653807334305259</v>
       </c>
       <c r="AJ3">
-        <v>0.7221103809777035</v>
+        <v>0.7477906186267845</v>
       </c>
       <c r="AK3">
-        <v>0.5319994403246117</v>
+        <v>0.5467516519501784</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0328</v>
+        <v>-0.00154</v>
       </c>
       <c r="E4">
-        <v>-0.0394</v>
+        <v>-0.0229</v>
       </c>
       <c r="F4">
-        <v>0.1</v>
+        <v>0.189</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,10 +862,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>461.2</v>
+        <v>343.5</v>
       </c>
       <c r="L4">
-        <v>0.3705608227542986</v>
+        <v>0.4235511713933415</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,55 +889,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>946.3</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.2353160590839011</v>
       </c>
       <c r="W4">
-        <v>0.09269792776314996</v>
+        <v>0.07011348791639452</v>
       </c>
       <c r="X4">
-        <v>0.07188173408198843</v>
+        <v>0.1198792521070177</v>
       </c>
       <c r="Y4">
-        <v>0.02081619368116153</v>
+        <v>-0.04976576419062316</v>
       </c>
       <c r="Z4">
-        <v>0.09409683370127316</v>
+        <v>0.05993378462266104</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04011113821510325</v>
+        <v>0.06376392103204979</v>
       </c>
       <c r="AC4">
-        <v>-0.04011113821510325</v>
+        <v>-0.06376392103204979</v>
       </c>
       <c r="AD4">
-        <v>8632.4</v>
+        <v>9363.6</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8632.4</v>
+        <v>9363.6</v>
       </c>
       <c r="AG4">
-        <v>8632.4</v>
+        <v>8417.300000000001</v>
       </c>
       <c r="AH4">
-        <v>0.6128702467838582</v>
+        <v>0.6995592080687337</v>
       </c>
       <c r="AI4">
-        <v>0.6379437760501345</v>
+        <v>0.7024403417828824</v>
       </c>
       <c r="AJ4">
-        <v>0.6128702467838582</v>
+        <v>0.676702549301776</v>
       </c>
       <c r="AK4">
-        <v>0.6379437760501345</v>
+        <v>0.6797025145754938</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0467</v>
+        <v>0.0323</v>
       </c>
       <c r="E5">
-        <v>0.109</v>
+        <v>0.0529</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-0.00749320693219249</v>
+        <v>-0.006238567565841862</v>
       </c>
       <c r="J5">
-        <v>-0.007451723751583196</v>
+        <v>-0.005523135505538897</v>
       </c>
       <c r="K5">
-        <v>93.8</v>
+        <v>92</v>
       </c>
       <c r="L5">
-        <v>0.3782258064516129</v>
+        <v>0.4105310129406515</v>
       </c>
       <c r="M5">
-        <v>9.119999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N5">
-        <v>0.007500616827041696</v>
+        <v>0.00671418873048201</v>
       </c>
       <c r="O5">
-        <v>0.09722814498933902</v>
+        <v>0.1075</v>
       </c>
       <c r="P5">
-        <v>9.119999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q5">
-        <v>0.007500616827041696</v>
+        <v>0.00671418873048201</v>
       </c>
       <c r="R5">
-        <v>0.09722814498933902</v>
+        <v>0.1075</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>95.40000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="V5">
-        <v>0.07846039970392302</v>
+        <v>0.04120841819416158</v>
       </c>
       <c r="W5">
-        <v>0.0459578637922587</v>
+        <v>0.04348031570490098</v>
       </c>
       <c r="X5">
-        <v>0.1158724608777484</v>
+        <v>0.1269401253991309</v>
       </c>
       <c r="Y5">
-        <v>-0.06991459708548972</v>
+        <v>-0.08345980969422992</v>
       </c>
       <c r="Z5">
-        <v>0.04024996150156333</v>
+        <v>0.03349690507862994</v>
       </c>
       <c r="AA5">
-        <v>-0.0002999315941215087</v>
+        <v>-0.0001850079457654472</v>
       </c>
       <c r="AB5">
-        <v>0.03983168418606838</v>
+        <v>0.06360276912402492</v>
       </c>
       <c r="AC5">
-        <v>-0.04013161578018988</v>
+        <v>-0.06378777706979037</v>
       </c>
       <c r="AD5">
-        <v>4659.9</v>
+        <v>3887.5</v>
       </c>
       <c r="AE5">
-        <v>12.29657659591869</v>
+        <v>9.770314957525807</v>
       </c>
       <c r="AF5">
-        <v>4672.196576595918</v>
+        <v>3897.270314957526</v>
       </c>
       <c r="AG5">
-        <v>4576.796576595919</v>
+        <v>3836.570314957526</v>
       </c>
       <c r="AH5">
-        <v>0.7934986316574739</v>
+        <v>0.7257121311198559</v>
       </c>
       <c r="AI5">
-        <v>0.682930235703522</v>
+        <v>0.6676071283045524</v>
       </c>
       <c r="AJ5">
-        <v>0.7900977577675017</v>
+        <v>0.7225764209487104</v>
       </c>
       <c r="AK5">
-        <v>0.6784463236276063</v>
+        <v>0.6641145974082668</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>7753.577371048253</v>
+        <v>6991.906474820144</v>
       </c>
       <c r="AP5">
-        <v>7615.302124119666</v>
+        <v>6900.306321866054</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Addiko Bank AG (WBAG:ADKO)</t>
+          <t>Erste Group Bank AG (WBAG:EBS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1090,6 +1090,15 @@
           <t>Bank (Money Center)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.0408</v>
+      </c>
+      <c r="E6">
+        <v>0.146</v>
+      </c>
+      <c r="F6">
+        <v>0.0999</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1103,82 +1112,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>20.2</v>
+        <v>2077.9</v>
       </c>
       <c r="L6">
-        <v>0.08201380430369468</v>
+        <v>0.2654581225407532</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1645.3</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.1264467637067892</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.7918090379710284</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>1158.1</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.08900382729522434</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.5573415467539342</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>487.2</v>
+      </c>
+      <c r="T6">
+        <v>0.2961162098097612</v>
       </c>
       <c r="U6">
-        <v>1376.7</v>
+        <v>7715</v>
       </c>
       <c r="V6">
-        <v>4.567684140676842</v>
+        <v>0.5929233465008685</v>
       </c>
       <c r="W6">
-        <v>0.02048889339689624</v>
+        <v>0.09690522604534899</v>
       </c>
       <c r="X6">
-        <v>0.04120143593450175</v>
+        <v>0.139797277469066</v>
       </c>
       <c r="Y6">
-        <v>-0.02071254253760551</v>
+        <v>-0.04289205142371696</v>
       </c>
       <c r="Z6">
-        <v>-1.411542208722562</v>
+        <v>0.1383569537290059</v>
       </c>
       <c r="AA6">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04104811182897827</v>
+        <v>0.06557576244537838</v>
       </c>
       <c r="AC6">
-        <v>-0.04104811182897827</v>
+        <v>-0.06557576244537838</v>
       </c>
       <c r="AD6">
-        <v>2.2</v>
+        <v>41946</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>41946</v>
       </c>
       <c r="AG6">
-        <v>-1374.5</v>
+        <v>34231</v>
       </c>
       <c r="AH6">
-        <v>0.007246376811594205</v>
+        <v>0.7632401588127617</v>
       </c>
       <c r="AI6">
-        <v>0.002222671246716509</v>
+        <v>0.6350383860160145</v>
       </c>
       <c r="AJ6">
-        <v>1.280868511788277</v>
+        <v>0.724576020049616</v>
       </c>
       <c r="AK6">
-        <v>3.552597570431636</v>
+        <v>0.5867732186904866</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Erste Group Bank AG (WBAG:EBS)</t>
+          <t>Oberbank AG (WBAG:OBS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,13 +1216,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.00792</v>
+        <v>-0.0116</v>
       </c>
       <c r="E7">
-        <v>0.0292</v>
-      </c>
-      <c r="F7">
-        <v>0.333</v>
+        <v>-0.105</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1225,28 +1234,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1851.4</v>
+        <v>115.5</v>
       </c>
       <c r="L7">
-        <v>0.2240671935323804</v>
+        <v>0.2301255230125523</v>
       </c>
       <c r="M7">
-        <v>392.4</v>
+        <v>43.4</v>
       </c>
       <c r="N7">
-        <v>0.02067199797705218</v>
+        <v>0.01122113917832303</v>
       </c>
       <c r="O7">
-        <v>0.2119477152425192</v>
+        <v>0.3757575757575757</v>
       </c>
       <c r="P7">
-        <v>392.4</v>
+        <v>43.4</v>
       </c>
       <c r="Q7">
-        <v>0.02067199797705218</v>
+        <v>0.01122113917832303</v>
       </c>
       <c r="R7">
-        <v>0.2119477152425192</v>
+        <v>0.3757575757575757</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1255,55 +1264,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>12112.9</v>
+        <v>94.2</v>
       </c>
       <c r="V7">
-        <v>0.6381188692564612</v>
+        <v>0.02435556015202834</v>
       </c>
       <c r="W7">
-        <v>0.09605188067444877</v>
+        <v>0.03067484662576687</v>
       </c>
       <c r="X7">
-        <v>0.08951786742619243</v>
+        <v>0.1200131781078022</v>
       </c>
       <c r="Y7">
-        <v>0.006534013248256337</v>
+        <v>-0.08933833148203534</v>
       </c>
       <c r="Z7">
-        <v>0.1564763051843772</v>
+        <v>0.03602446131982027</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.04105862715688245</v>
+        <v>0.06679341903725929</v>
       </c>
       <c r="AC7">
-        <v>-0.04105862715688245</v>
+        <v>-0.06679341903725929</v>
       </c>
       <c r="AD7">
-        <v>47245.7</v>
+        <v>9029</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>47245.7</v>
+        <v>9029</v>
       </c>
       <c r="AG7">
-        <v>35132.8</v>
+        <v>8934.799999999999</v>
       </c>
       <c r="AH7">
-        <v>0.7133806145144267</v>
+        <v>0.7001015763722502</v>
       </c>
       <c r="AI7">
-        <v>0.6298712812547911</v>
+        <v>0.7328912230005601</v>
       </c>
       <c r="AJ7">
-        <v>0.6492247990390834</v>
+        <v>0.6978949423940636</v>
       </c>
       <c r="AK7">
-        <v>0.5585891540902702</v>
+        <v>0.7308330947609504</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1320,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Oberbank AG (WBAG:OBS)</t>
+          <t>Raiffeisen Bank International AG (WBAG:RBI)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1329,10 +1338,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0459</v>
+        <v>0.108</v>
       </c>
       <c r="E8">
-        <v>0.0683</v>
+        <v>0.261</v>
+      </c>
+      <c r="F8">
+        <v>0.05400000000000001</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1347,215 +1359,87 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>274.3</v>
+        <v>3057.5</v>
       </c>
       <c r="L8">
-        <v>0.3923616077814333</v>
+        <v>0.4060478890821924</v>
       </c>
       <c r="M8">
-        <v>33.8</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.009250389994252716</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.1232227488151659</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>33.8</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.009250389994252716</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.1232227488151659</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>182.7</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>0.05000136840088672</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.07778250389905006</v>
+        <v>0.182371817813089</v>
       </c>
       <c r="X8">
-        <v>0.09620627702572242</v>
+        <v>0.165072661652127</v>
       </c>
       <c r="Y8">
-        <v>-0.01842377312667236</v>
+        <v>0.01729915616096198</v>
       </c>
       <c r="Z8">
-        <v>0.05200476084207394</v>
+        <v>0.6775270384566933</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04165281332604674</v>
+        <v>0.06782245406715771</v>
       </c>
       <c r="AC8">
-        <v>-0.04165281332604674</v>
+        <v>-0.06782245406715771</v>
       </c>
       <c r="AD8">
-        <v>10349.6</v>
+        <v>23551.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>10349.6</v>
+        <v>23551.7</v>
       </c>
       <c r="AG8">
-        <v>10166.9</v>
+        <v>23551.7</v>
       </c>
       <c r="AH8">
-        <v>0.739072374763452</v>
+        <v>0.8134234539162389</v>
       </c>
       <c r="AI8">
-        <v>0.7327928629588983</v>
+        <v>0.5708520472839825</v>
       </c>
       <c r="AJ8">
-        <v>0.7356231187774948</v>
+        <v>0.8134234539162389</v>
       </c>
       <c r="AK8">
-        <v>0.7292910019511075</v>
+        <v>0.5708520472839825</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Raiffeisen Bank International AG (WBAG:RBI)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>0.06660000000000001</v>
-      </c>
-      <c r="E9">
-        <v>0.322</v>
-      </c>
-      <c r="F9">
-        <v>0.201</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>1460.1</v>
-      </c>
-      <c r="L9">
-        <v>0.2435692122910619</v>
-      </c>
-      <c r="M9">
-        <v>295.91</v>
-      </c>
-      <c r="N9">
-        <v>0.03073016730188072</v>
-      </c>
-      <c r="O9">
-        <v>0.2026642010821177</v>
-      </c>
-      <c r="P9">
-        <v>287.1</v>
-      </c>
-      <c r="Q9">
-        <v>0.02981525136821992</v>
-      </c>
-      <c r="R9">
-        <v>0.1966303677830286</v>
-      </c>
-      <c r="S9">
-        <v>8.810000000000002</v>
-      </c>
-      <c r="T9">
-        <v>0.02977256598290021</v>
-      </c>
-      <c r="U9">
-        <v>49684.7</v>
-      </c>
-      <c r="V9">
-        <v>5.15974162192475</v>
-      </c>
-      <c r="W9">
-        <v>0.09380059103173582</v>
-      </c>
-      <c r="X9">
-        <v>0.1303551690428193</v>
-      </c>
-      <c r="Y9">
-        <v>-0.03655457801108347</v>
-      </c>
-      <c r="Z9">
-        <v>-1.371605079510354</v>
-      </c>
-      <c r="AA9">
-        <v>-0</v>
-      </c>
-      <c r="AB9">
-        <v>0.04263255206318442</v>
-      </c>
-      <c r="AC9">
-        <v>-0.04263255206318442</v>
-      </c>
-      <c r="AD9">
-        <v>44164.3</v>
-      </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>44164.3</v>
-      </c>
-      <c r="AG9">
-        <v>-5520.399999999994</v>
-      </c>
-      <c r="AH9">
-        <v>0.8209954344011183</v>
-      </c>
-      <c r="AI9">
-        <v>0.7117373661190561</v>
-      </c>
-      <c r="AJ9">
-        <v>-1.343522597288809</v>
-      </c>
-      <c r="AK9">
-        <v>-0.4463923277834824</v>
-      </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03655</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="E2">
-        <v>0.059</v>
+        <v>0.127</v>
       </c>
       <c r="F2">
-        <v>0.0999</v>
+        <v>0.145</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-8.166208091688492e-05</v>
+        <v>-0.0001121947182774198</v>
       </c>
       <c r="J2">
-        <v>-6.756730813059875e-05</v>
+        <v>-9.099648295568901e-05</v>
       </c>
       <c r="K2">
-        <v>5764.6</v>
+        <v>4516.7</v>
       </c>
       <c r="L2">
-        <v>0.3367153229245157</v>
+        <v>0.3324672074432847</v>
       </c>
       <c r="M2">
-        <v>1713.187</v>
+        <v>1019.39</v>
       </c>
       <c r="N2">
-        <v>0.06030925802715556</v>
+        <v>0.03589856460678114</v>
       </c>
       <c r="O2">
-        <v>0.2971909586094438</v>
+        <v>0.2256935373170678</v>
       </c>
       <c r="P2">
-        <v>1225.69</v>
+        <v>1017.8</v>
       </c>
       <c r="Q2">
-        <v>0.04314791932889071</v>
+        <v>0.03584257159358228</v>
       </c>
       <c r="R2">
-        <v>0.212623599208965</v>
+        <v>0.2253415103947572</v>
       </c>
       <c r="S2">
-        <v>487.4970000000001</v>
+        <v>1.590000000000002</v>
       </c>
       <c r="T2">
-        <v>0.2845556264435815</v>
+        <v>0.001559756324860948</v>
       </c>
       <c r="U2">
-        <v>8962.799999999999</v>
+        <v>5749.2</v>
       </c>
       <c r="V2">
-        <v>0.3155171139203075</v>
+        <v>0.2024622839514868</v>
       </c>
       <c r="W2">
-        <v>0.05842793343817335</v>
+        <v>0.160169336663215</v>
       </c>
       <c r="X2">
-        <v>0.1330762479018652</v>
+        <v>0.09841513182006344</v>
       </c>
       <c r="Y2">
-        <v>-0.07464831446369183</v>
+        <v>0.06175420484315151</v>
       </c>
       <c r="Z2">
-        <v>0.162349586393769</v>
+        <v>0.1572925297306434</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0646698417387141</v>
+        <v>0.05521652901992886</v>
       </c>
       <c r="AC2">
-        <v>-0.06468176975758438</v>
+        <v>-0.05542648352481279</v>
       </c>
       <c r="AD2">
-        <v>89794.39999999999</v>
+        <v>83148.8</v>
       </c>
       <c r="AE2">
-        <v>9.770314957525807</v>
+        <v>10.58105062843029</v>
       </c>
       <c r="AF2">
-        <v>89804.17031495753</v>
+        <v>83159.38105062844</v>
       </c>
       <c r="AG2">
-        <v>80841.37031495753</v>
+        <v>77410.18105062844</v>
       </c>
       <c r="AH2">
-        <v>0.7596946886160805</v>
+        <v>0.7454511121470918</v>
       </c>
       <c r="AI2">
-        <v>0.6308064254996384</v>
+        <v>0.6646349727545907</v>
       </c>
       <c r="AJ2">
-        <v>0.7399798466178423</v>
+        <v>0.7316197185654044</v>
       </c>
       <c r="AK2">
-        <v>0.6060015030148722</v>
+        <v>0.6484829953872766</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>161500.7194244604</v>
+        <v>140454.0540540541</v>
       </c>
       <c r="AP2">
-        <v>145398.1480484848</v>
+        <v>130760.4409638994</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BKS Bank AG (WBAG:BKS)</t>
+          <t>BAWAG Group AG (WBAG:BG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.045</v>
+        <v>0.06709999999999999</v>
       </c>
       <c r="E3">
-        <v>0.06509999999999999</v>
+        <v>0.05980000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.174</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,85 +740,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>78.2</v>
+        <v>675.2</v>
       </c>
       <c r="L3">
-        <v>0.3466312056737589</v>
+        <v>0.4787973337115303</v>
       </c>
       <c r="M3">
-        <v>14.597</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0231441255747582</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.1866624040920716</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>14.3</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02267322023148882</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.1828644501278772</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>0.2970000000000006</v>
-      </c>
-      <c r="T3">
-        <v>0.0203466465712133</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>146.6</v>
+        <v>644.6</v>
       </c>
       <c r="V3">
-        <v>0.2324401458696686</v>
+        <v>0.1476882188516702</v>
       </c>
       <c r="W3">
-        <v>0.04674237895995218</v>
+        <v>0.1704361873990307</v>
       </c>
       <c r="X3">
-        <v>0.1392123704045994</v>
+        <v>0.1111956255778351</v>
       </c>
       <c r="Y3">
-        <v>-0.09246999144464726</v>
+        <v>0.05924056182119558</v>
       </c>
       <c r="Z3">
-        <v>0.06251212280750366</v>
+        <v>0.1139196536041167</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06338066233987308</v>
+        <v>0.0544660699078329</v>
       </c>
       <c r="AC3">
-        <v>-0.06338066233987308</v>
+        <v>-0.0544660699078329</v>
       </c>
       <c r="AD3">
-        <v>2016.6</v>
+        <v>14629.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2016.6</v>
+        <v>14629.6</v>
       </c>
       <c r="AG3">
-        <v>1870</v>
+        <v>13985</v>
       </c>
       <c r="AH3">
-        <v>0.7617572621161183</v>
+        <v>0.7702140653462636</v>
       </c>
       <c r="AI3">
-        <v>0.5653807334305259</v>
+        <v>0.7682322298773315</v>
       </c>
       <c r="AJ3">
-        <v>0.7477906186267845</v>
+        <v>0.7621419540480447</v>
       </c>
       <c r="AK3">
-        <v>0.5467516519501784</v>
+        <v>0.7601121824486646</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BAWAG Group AG (WBAG:BG)</t>
+          <t>BKS Bank AG (WBAG:BKS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,13 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.00154</v>
+        <v>0.09699999999999999</v>
       </c>
       <c r="E4">
-        <v>-0.0229</v>
-      </c>
-      <c r="F4">
-        <v>0.189</v>
+        <v>0.155</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,82 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>343.5</v>
+        <v>157.2</v>
       </c>
       <c r="L4">
-        <v>0.4235511713933415</v>
+        <v>0.4660539579009783</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>16.99</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02227612429526682</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1080788804071247</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>15.4</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02019142519994755</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.0979643765903308</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.590000000000002</v>
+      </c>
+      <c r="T4">
+        <v>0.09358446144791062</v>
       </c>
       <c r="U4">
-        <v>946.3</v>
+        <v>39.6</v>
       </c>
       <c r="V4">
-        <v>0.2353160590839011</v>
+        <v>0.051920807657008</v>
       </c>
       <c r="W4">
-        <v>0.07011348791639452</v>
+        <v>0.1014062701586892</v>
       </c>
       <c r="X4">
-        <v>0.1198792521070177</v>
+        <v>0.09841513182006344</v>
       </c>
       <c r="Y4">
-        <v>-0.04976576419062316</v>
+        <v>0.002991138338625757</v>
       </c>
       <c r="Z4">
-        <v>0.05993378462266104</v>
+        <v>0.09861996374481025</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06376392103204979</v>
+        <v>0.05479650359840669</v>
       </c>
       <c r="AC4">
-        <v>-0.06376392103204979</v>
+        <v>-0.05479650359840669</v>
       </c>
       <c r="AD4">
-        <v>9363.6</v>
+        <v>1928</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>9363.6</v>
+        <v>1928</v>
       </c>
       <c r="AG4">
-        <v>8417.300000000001</v>
+        <v>1888.4</v>
       </c>
       <c r="AH4">
-        <v>0.6995592080687337</v>
+        <v>0.7165421637492103</v>
       </c>
       <c r="AI4">
-        <v>0.7024403417828824</v>
+        <v>0.5144488619686741</v>
       </c>
       <c r="AJ4">
-        <v>0.676702549301776</v>
+        <v>0.7123080985251404</v>
       </c>
       <c r="AK4">
-        <v>0.6797025145754938</v>
+        <v>0.5092635042204903</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0323</v>
+        <v>0.105</v>
       </c>
       <c r="E5">
-        <v>0.0529</v>
+        <v>0.11</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-0.006238567565841862</v>
+        <v>-0.004066729257433454</v>
       </c>
       <c r="J5">
-        <v>-0.005523135505538897</v>
+        <v>-0.003209582050899198</v>
       </c>
       <c r="K5">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="L5">
-        <v>0.4105310129406515</v>
+        <v>0.4429028815368196</v>
       </c>
       <c r="M5">
-        <v>9.890000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="N5">
-        <v>0.00671418873048201</v>
+        <v>0.006995247503604421</v>
       </c>
       <c r="O5">
-        <v>0.1075</v>
+        <v>0.0789156626506024</v>
       </c>
       <c r="P5">
-        <v>9.890000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="Q5">
-        <v>0.00671418873048201</v>
+        <v>0.006995247503604421</v>
       </c>
       <c r="R5">
-        <v>0.1075</v>
+        <v>0.0789156626506024</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1011,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>60.7</v>
+        <v>45.6</v>
       </c>
       <c r="V5">
-        <v>0.04120841819416158</v>
+        <v>0.02434986917285203</v>
       </c>
       <c r="W5">
-        <v>0.04348031570490098</v>
+        <v>0.08772856991861325</v>
       </c>
       <c r="X5">
-        <v>0.1269401253991309</v>
+        <v>0.0878003227767052</v>
       </c>
       <c r="Y5">
-        <v>-0.08345980969422992</v>
+        <v>-7.175285809195298e-05</v>
       </c>
       <c r="Z5">
-        <v>0.03349690507862994</v>
+        <v>0.06541490497963919</v>
       </c>
       <c r="AA5">
-        <v>-0.0001850079457654472</v>
+        <v>-0.0002099545048839265</v>
       </c>
       <c r="AB5">
-        <v>0.06360276912402492</v>
+        <v>0.05521652901992886</v>
       </c>
       <c r="AC5">
-        <v>-0.06378777706979037</v>
+        <v>-0.05542648352481279</v>
       </c>
       <c r="AD5">
-        <v>3887.5</v>
+        <v>3441.7</v>
       </c>
       <c r="AE5">
-        <v>9.770314957525807</v>
+        <v>10.58105062843029</v>
       </c>
       <c r="AF5">
-        <v>3897.270314957526</v>
+        <v>3452.28105062843</v>
       </c>
       <c r="AG5">
-        <v>3836.570314957526</v>
+        <v>3406.68105062843</v>
       </c>
       <c r="AH5">
-        <v>0.7257121311198559</v>
+        <v>0.6483179973421703</v>
       </c>
       <c r="AI5">
-        <v>0.6676071283045524</v>
+        <v>0.5918654984840611</v>
       </c>
       <c r="AJ5">
-        <v>0.7225764209487104</v>
+        <v>0.6452803875982615</v>
       </c>
       <c r="AK5">
-        <v>0.6641145974082668</v>
+        <v>0.588649664812547</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1068,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>6991.906474820144</v>
+        <v>5813.682432432433</v>
       </c>
       <c r="AP5">
-        <v>6900.306321866054</v>
+        <v>5754.528801737213</v>
       </c>
     </row>
     <row r="6">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0408</v>
+        <v>0.0723</v>
       </c>
       <c r="E6">
-        <v>0.146</v>
+        <v>0.127</v>
       </c>
       <c r="F6">
-        <v>0.0999</v>
+        <v>0.116</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,85 +1112,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>2077.9</v>
+        <v>2992.4</v>
       </c>
       <c r="L6">
-        <v>0.2654581225407532</v>
+        <v>0.286282838719553</v>
       </c>
       <c r="M6">
-        <v>1645.3</v>
+        <v>932</v>
       </c>
       <c r="N6">
-        <v>0.1264467637067892</v>
+        <v>0.05690942730309155</v>
       </c>
       <c r="O6">
-        <v>0.7918090379710284</v>
+        <v>0.3114556877422804</v>
       </c>
       <c r="P6">
-        <v>1158.1</v>
+        <v>932</v>
       </c>
       <c r="Q6">
-        <v>0.08900382729522434</v>
+        <v>0.05690942730309155</v>
       </c>
       <c r="R6">
-        <v>0.5573415467539342</v>
+        <v>0.3114556877422804</v>
       </c>
       <c r="S6">
-        <v>487.2</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.2961162098097612</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>7715</v>
+        <v>4941.4</v>
       </c>
       <c r="V6">
-        <v>0.5929233465008685</v>
+        <v>0.3017298756174856</v>
       </c>
       <c r="W6">
-        <v>0.09690522604534899</v>
+        <v>0.1626976359800787</v>
       </c>
       <c r="X6">
-        <v>0.139797277469066</v>
+        <v>0.1107055697400653</v>
       </c>
       <c r="Y6">
-        <v>-0.04289205142371696</v>
+        <v>0.0519920662400134</v>
       </c>
       <c r="Z6">
-        <v>0.1383569537290059</v>
+        <v>0.1986302671435141</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.06557576244537838</v>
+        <v>0.0562199113249665</v>
       </c>
       <c r="AC6">
-        <v>-0.06557576244537838</v>
+        <v>-0.0562199113249665</v>
       </c>
       <c r="AD6">
-        <v>41946</v>
+        <v>54375.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>41946</v>
+        <v>54375.9</v>
       </c>
       <c r="AG6">
-        <v>34231</v>
+        <v>49434.5</v>
       </c>
       <c r="AH6">
-        <v>0.7632401588127617</v>
+        <v>0.7685335421354349</v>
       </c>
       <c r="AI6">
-        <v>0.6350383860160145</v>
+        <v>0.6498029411835001</v>
       </c>
       <c r="AJ6">
-        <v>0.724576020049616</v>
+        <v>0.7511540553764242</v>
       </c>
       <c r="AK6">
-        <v>0.5867732186904866</v>
+        <v>0.6278257843615379</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0116</v>
+        <v>0.118</v>
       </c>
       <c r="E7">
-        <v>-0.105</v>
+        <v>0.17</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,28 +1234,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>115.5</v>
+        <v>525.9</v>
       </c>
       <c r="L7">
-        <v>0.2301255230125523</v>
+        <v>0.5204354280059377</v>
       </c>
       <c r="M7">
-        <v>43.4</v>
+        <v>57.3</v>
       </c>
       <c r="N7">
-        <v>0.01122113917832303</v>
+        <v>0.01141547962944516</v>
       </c>
       <c r="O7">
-        <v>0.3757575757575757</v>
+        <v>0.1089560752994866</v>
       </c>
       <c r="P7">
-        <v>43.4</v>
+        <v>57.3</v>
       </c>
       <c r="Q7">
-        <v>0.01122113917832303</v>
+        <v>0.01141547962944516</v>
       </c>
       <c r="R7">
-        <v>0.3757575757575757</v>
+        <v>0.1089560752994866</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1264,182 +1264,60 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>94.2</v>
+        <v>78</v>
       </c>
       <c r="V7">
-        <v>0.02435556015202834</v>
+        <v>0.01553939635421855</v>
       </c>
       <c r="W7">
-        <v>0.03067484662576687</v>
+        <v>0.160169336663215</v>
       </c>
       <c r="X7">
-        <v>0.1200131781078022</v>
+        <v>0.08631795633844351</v>
       </c>
       <c r="Y7">
-        <v>-0.08933833148203534</v>
+        <v>0.07385138032477144</v>
       </c>
       <c r="Z7">
-        <v>0.03602446131982027</v>
+        <v>0.08270449002308033</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.06679341903725929</v>
+        <v>0.05745613080935483</v>
       </c>
       <c r="AC7">
-        <v>-0.06679341903725929</v>
+        <v>-0.05745613080935483</v>
       </c>
       <c r="AD7">
-        <v>9029</v>
+        <v>8773.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>9029</v>
+        <v>8773.6</v>
       </c>
       <c r="AG7">
-        <v>8934.799999999999</v>
+        <v>8695.6</v>
       </c>
       <c r="AH7">
-        <v>0.7001015763722502</v>
+        <v>0.6360861590215398</v>
       </c>
       <c r="AI7">
-        <v>0.7328912230005601</v>
+        <v>0.68458177278402</v>
       </c>
       <c r="AJ7">
-        <v>0.6978949423940636</v>
+        <v>0.6340165219356767</v>
       </c>
       <c r="AK7">
-        <v>0.7308330947609504</v>
+        <v>0.6826503375726174</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Raiffeisen Bank International AG (WBAG:RBI)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.108</v>
-      </c>
-      <c r="E8">
-        <v>0.261</v>
-      </c>
-      <c r="F8">
-        <v>0.05400000000000001</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>3057.5</v>
-      </c>
-      <c r="L8">
-        <v>0.4060478890821924</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>-0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>-0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>0</v>
-      </c>
-      <c r="V8">
-        <v>0</v>
-      </c>
-      <c r="W8">
-        <v>0.182371817813089</v>
-      </c>
-      <c r="X8">
-        <v>0.165072661652127</v>
-      </c>
-      <c r="Y8">
-        <v>0.01729915616096198</v>
-      </c>
-      <c r="Z8">
-        <v>0.6775270384566933</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.06782245406715771</v>
-      </c>
-      <c r="AC8">
-        <v>-0.06782245406715771</v>
-      </c>
-      <c r="AD8">
-        <v>23551.7</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>23551.7</v>
-      </c>
-      <c r="AG8">
-        <v>23551.7</v>
-      </c>
-      <c r="AH8">
-        <v>0.8134234539162389</v>
-      </c>
-      <c r="AI8">
-        <v>0.5708520472839825</v>
-      </c>
-      <c r="AJ8">
-        <v>0.8134234539162389</v>
-      </c>
-      <c r="AK8">
-        <v>0.5708520472839825</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09699999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="E2">
-        <v>0.127</v>
+        <v>0.1405</v>
       </c>
       <c r="F2">
-        <v>0.145</v>
+        <v>0.0455</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-0.0001121947182774198</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>-9.099648295568901e-05</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>4516.7</v>
+        <v>6808.5</v>
       </c>
       <c r="L2">
-        <v>0.3324672074432847</v>
+        <v>0.2981816111485805</v>
       </c>
       <c r="M2">
-        <v>1019.39</v>
+        <v>2326.558</v>
       </c>
       <c r="N2">
-        <v>0.03589856460678114</v>
+        <v>0.06206836019827232</v>
       </c>
       <c r="O2">
-        <v>0.2256935373170678</v>
+        <v>0.341713740177719</v>
       </c>
       <c r="P2">
-        <v>1017.8</v>
+        <v>2299.3</v>
       </c>
       <c r="Q2">
-        <v>0.03584257159358228</v>
+        <v>0.06134116605040044</v>
       </c>
       <c r="R2">
-        <v>0.2253415103947572</v>
+        <v>0.3377102151722112</v>
       </c>
       <c r="S2">
-        <v>1.590000000000002</v>
+        <v>27.25799999999995</v>
       </c>
       <c r="T2">
-        <v>0.001559756324860948</v>
+        <v>0.01171601997457186</v>
       </c>
       <c r="U2">
-        <v>5749.2</v>
+        <v>51297</v>
       </c>
       <c r="V2">
-        <v>0.2024622839514868</v>
+        <v>1.368511196837034</v>
       </c>
       <c r="W2">
-        <v>0.160169336663215</v>
+        <v>0.1228218896876897</v>
       </c>
       <c r="X2">
-        <v>0.09841513182006344</v>
+        <v>0.1075489169108462</v>
       </c>
       <c r="Y2">
-        <v>0.06175420484315151</v>
+        <v>0.0152729727768435</v>
       </c>
       <c r="Z2">
-        <v>0.1572925297306434</v>
+        <v>0.2535894838784196</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05521652901992886</v>
+        <v>0.0607505882071487</v>
       </c>
       <c r="AC2">
-        <v>-0.05542648352481279</v>
+        <v>-0.0607505882071487</v>
       </c>
       <c r="AD2">
-        <v>83148.8</v>
+        <v>118409.6</v>
       </c>
       <c r="AE2">
-        <v>10.58105062843029</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>83159.38105062844</v>
+        <v>118409.6</v>
       </c>
       <c r="AG2">
-        <v>77410.18105062844</v>
+        <v>67112.59999999999</v>
       </c>
       <c r="AH2">
-        <v>0.7454511121470918</v>
+        <v>0.7595549266357652</v>
       </c>
       <c r="AI2">
-        <v>0.6646349727545907</v>
+        <v>0.6498042239337956</v>
       </c>
       <c r="AJ2">
-        <v>0.7316197185654044</v>
+        <v>0.641633937688104</v>
       </c>
       <c r="AK2">
-        <v>0.6484829953872766</v>
+        <v>0.5125975260928841</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>140454.0540540541</v>
-      </c>
-      <c r="AP2">
-        <v>130760.4409638994</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BAWAG Group AG (WBAG:BG)</t>
+          <t>Erste Group Bank AG (WBAG:EBS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.06709999999999999</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E3">
-        <v>0.05980000000000001</v>
+        <v>0.124</v>
       </c>
       <c r="F3">
-        <v>0.174</v>
+        <v>0.068</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -740,82 +734,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>675.2</v>
+        <v>3573.5</v>
       </c>
       <c r="L3">
-        <v>0.4787973337115303</v>
+        <v>0.3000848147930436</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1349.6</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.05416751955625659</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.3776689520078355</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1322.8</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.05309187527342637</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.3701693018049531</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>26.79999999999995</v>
+      </c>
+      <c r="T3">
+        <v>0.01985773562537045</v>
       </c>
       <c r="U3">
-        <v>644.6</v>
+        <v>7317.6</v>
       </c>
       <c r="V3">
-        <v>0.1476882188516702</v>
+        <v>0.2936990523894956</v>
       </c>
       <c r="W3">
-        <v>0.1704361873990307</v>
+        <v>0.1606572854381154</v>
       </c>
       <c r="X3">
-        <v>0.1111956255778351</v>
+        <v>0.1049092666594396</v>
       </c>
       <c r="Y3">
-        <v>0.05924056182119558</v>
+        <v>0.05574801877867576</v>
       </c>
       <c r="Z3">
-        <v>0.1139196536041167</v>
+        <v>0.1661372118168184</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0544660699078329</v>
+        <v>0.0600226171939829</v>
       </c>
       <c r="AC3">
-        <v>-0.0544660699078329</v>
+        <v>-0.0600226171939829</v>
       </c>
       <c r="AD3">
-        <v>14629.6</v>
+        <v>68381.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>14629.6</v>
+        <v>68381.7</v>
       </c>
       <c r="AG3">
-        <v>13985</v>
+        <v>61064.1</v>
       </c>
       <c r="AH3">
-        <v>0.7702140653462636</v>
+        <v>0.7329463969902569</v>
       </c>
       <c r="AI3">
-        <v>0.7682322298773315</v>
+        <v>0.6706297368544932</v>
       </c>
       <c r="AJ3">
-        <v>0.7621419540480447</v>
+        <v>0.7102177963558713</v>
       </c>
       <c r="AK3">
-        <v>0.7601121824486646</v>
+        <v>0.6451650734082208</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BKS Bank AG (WBAG:BKS)</t>
+          <t>Raiffeisen Bank International AG (WBAG:RBI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,10 +838,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09699999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="E4">
-        <v>0.155</v>
+        <v>0.194</v>
+      </c>
+      <c r="F4">
+        <v>0.023</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>157.2</v>
+        <v>2626.6</v>
       </c>
       <c r="L4">
-        <v>0.4660539579009783</v>
+        <v>0.2744446534177585</v>
       </c>
       <c r="M4">
-        <v>16.99</v>
+        <v>872.2</v>
       </c>
       <c r="N4">
-        <v>0.02227612429526682</v>
+        <v>0.1298728371899104</v>
       </c>
       <c r="O4">
-        <v>0.1080788804071247</v>
+        <v>0.3320642655904972</v>
       </c>
       <c r="P4">
-        <v>15.4</v>
+        <v>872.2</v>
       </c>
       <c r="Q4">
-        <v>0.02019142519994755</v>
+        <v>0.1298728371899104</v>
       </c>
       <c r="R4">
-        <v>0.0979643765903308</v>
+        <v>0.3320642655904972</v>
       </c>
       <c r="S4">
-        <v>1.590000000000002</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.09358446144791062</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>39.6</v>
+        <v>43855.7</v>
       </c>
       <c r="V4">
-        <v>0.051920807657008</v>
+        <v>6.530227225349176</v>
       </c>
       <c r="W4">
-        <v>0.1014062701586892</v>
+        <v>0.13342747998537</v>
       </c>
       <c r="X4">
-        <v>0.09841513182006344</v>
+        <v>0.1498315502968729</v>
       </c>
       <c r="Y4">
-        <v>0.002991138338625757</v>
+        <v>-0.01640407031150284</v>
       </c>
       <c r="Z4">
-        <v>0.09861996374481025</v>
+        <v>4.968384986762198</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05479650359840669</v>
+        <v>0.06037845629967815</v>
       </c>
       <c r="AC4">
-        <v>-0.05479650359840669</v>
+        <v>-0.06037845629967815</v>
       </c>
       <c r="AD4">
-        <v>1928</v>
+        <v>39155.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1928</v>
+        <v>39155.7</v>
       </c>
       <c r="AG4">
-        <v>1888.4</v>
+        <v>-4700</v>
       </c>
       <c r="AH4">
-        <v>0.7165421637492103</v>
+        <v>0.8535953696739805</v>
       </c>
       <c r="AI4">
-        <v>0.5144488619686741</v>
+        <v>0.624135463108045</v>
       </c>
       <c r="AJ4">
-        <v>0.7123080985251404</v>
+        <v>-2.331580513939875</v>
       </c>
       <c r="AK4">
-        <v>0.5092635042204903</v>
+        <v>-0.2489380409105836</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bank für Tirol und Vorarlberg AG (WBAG:BTS)</t>
+          <t>Oberbank AG (WBAG:OBS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.105</v>
+        <v>0.0746</v>
       </c>
       <c r="E5">
-        <v>0.11</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,34 +975,34 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-0.004066729257433454</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-0.003209582050899198</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>166</v>
+        <v>404.2</v>
       </c>
       <c r="L5">
-        <v>0.4429028815368196</v>
+        <v>0.4315148927084445</v>
       </c>
       <c r="M5">
-        <v>13.1</v>
+        <v>82</v>
       </c>
       <c r="N5">
-        <v>0.006995247503604421</v>
+        <v>0.01606960884220428</v>
       </c>
       <c r="O5">
-        <v>0.0789156626506024</v>
+        <v>0.2028698664027709</v>
       </c>
       <c r="P5">
-        <v>13.1</v>
+        <v>82</v>
       </c>
       <c r="Q5">
-        <v>0.006995247503604421</v>
+        <v>0.01606960884220428</v>
       </c>
       <c r="R5">
-        <v>0.0789156626506024</v>
+        <v>0.2028698664027709</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,67 +1011,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>45.6</v>
+        <v>83</v>
       </c>
       <c r="V5">
-        <v>0.02434986917285203</v>
+        <v>0.01626557968174335</v>
       </c>
       <c r="W5">
-        <v>0.08772856991861325</v>
+        <v>0.1002157042620187</v>
       </c>
       <c r="X5">
-        <v>0.0878003227767052</v>
+        <v>0.0893243630570468</v>
       </c>
       <c r="Y5">
-        <v>-7.175285809195298e-05</v>
+        <v>0.01089134120497189</v>
       </c>
       <c r="Z5">
-        <v>0.06541490497963919</v>
+        <v>0.07358844833410585</v>
       </c>
       <c r="AA5">
-        <v>-0.0002099545048839265</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05521652901992886</v>
+        <v>0.06112272011461925</v>
       </c>
       <c r="AC5">
-        <v>-0.05542648352481279</v>
+        <v>-0.06112272011461925</v>
       </c>
       <c r="AD5">
-        <v>3441.7</v>
+        <v>8542.1</v>
       </c>
       <c r="AE5">
-        <v>10.58105062843029</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>3452.28105062843</v>
+        <v>8542.1</v>
       </c>
       <c r="AG5">
-        <v>3406.68105062843</v>
+        <v>8459.1</v>
       </c>
       <c r="AH5">
-        <v>0.6483179973421703</v>
+        <v>0.6260287726549846</v>
       </c>
       <c r="AI5">
-        <v>0.5918654984840611</v>
+        <v>0.6532605287509273</v>
       </c>
       <c r="AJ5">
-        <v>0.6452803875982615</v>
+        <v>0.6237400364255745</v>
       </c>
       <c r="AK5">
-        <v>0.588649664812547</v>
+        <v>0.6510455549483957</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>5813.682432432433</v>
-      </c>
-      <c r="AP5">
-        <v>5754.528801737213</v>
       </c>
     </row>
     <row r="6">
@@ -1082,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Erste Group Bank AG (WBAG:EBS)</t>
+          <t>BKS Bank AG (WBAG:BKS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1091,13 +1085,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0723</v>
+        <v>0.108</v>
       </c>
       <c r="E6">
-        <v>0.127</v>
-      </c>
-      <c r="F6">
-        <v>0.116</v>
+        <v>0.157</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1112,212 +1103,90 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>2992.4</v>
+        <v>204.2</v>
       </c>
       <c r="L6">
-        <v>0.286282838719553</v>
+        <v>0.488750598372427</v>
       </c>
       <c r="M6">
-        <v>932</v>
+        <v>22.758</v>
       </c>
       <c r="N6">
-        <v>0.05690942730309155</v>
+        <v>0.03034804640618749</v>
       </c>
       <c r="O6">
-        <v>0.3114556877422804</v>
+        <v>0.1114495592556317</v>
       </c>
       <c r="P6">
-        <v>932</v>
+        <v>22.3</v>
       </c>
       <c r="Q6">
-        <v>0.05690942730309155</v>
+        <v>0.02973729830644086</v>
       </c>
       <c r="R6">
-        <v>0.3114556877422804</v>
+        <v>0.1092066601371205</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.4579999999999984</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.02012479128218642</v>
       </c>
       <c r="U6">
-        <v>4941.4</v>
+        <v>40.7</v>
       </c>
       <c r="V6">
-        <v>0.3017298756174856</v>
+        <v>0.05427390318709162</v>
       </c>
       <c r="W6">
-        <v>0.1626976359800787</v>
+        <v>0.1122162993900093</v>
       </c>
       <c r="X6">
-        <v>0.1107055697400653</v>
+        <v>0.1101885671622528</v>
       </c>
       <c r="Y6">
-        <v>0.0519920662400134</v>
+        <v>0.002027732227756582</v>
       </c>
       <c r="Z6">
-        <v>0.1986302671435141</v>
+        <v>0.1126722580297187</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.0562199113249665</v>
+        <v>0.06153132713016055</v>
       </c>
       <c r="AC6">
-        <v>-0.0562199113249665</v>
+        <v>-0.06153132713016055</v>
       </c>
       <c r="AD6">
-        <v>54375.9</v>
+        <v>2330.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>54375.9</v>
+        <v>2330.1</v>
       </c>
       <c r="AG6">
-        <v>49434.5</v>
+        <v>2289.4</v>
       </c>
       <c r="AH6">
-        <v>0.7685335421354349</v>
+        <v>0.756525974025974</v>
       </c>
       <c r="AI6">
-        <v>0.6498029411835001</v>
+        <v>0.5241951812107714</v>
       </c>
       <c r="AJ6">
-        <v>0.7511540553764242</v>
+        <v>0.7532655545684861</v>
       </c>
       <c r="AK6">
-        <v>0.6278257843615379</v>
+        <v>0.5197983834347472</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Oberbank AG (WBAG:OBS)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.118</v>
-      </c>
-      <c r="E7">
-        <v>0.17</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>525.9</v>
-      </c>
-      <c r="L7">
-        <v>0.5204354280059377</v>
-      </c>
-      <c r="M7">
-        <v>57.3</v>
-      </c>
-      <c r="N7">
-        <v>0.01141547962944516</v>
-      </c>
-      <c r="O7">
-        <v>0.1089560752994866</v>
-      </c>
-      <c r="P7">
-        <v>57.3</v>
-      </c>
-      <c r="Q7">
-        <v>0.01141547962944516</v>
-      </c>
-      <c r="R7">
-        <v>0.1089560752994866</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>78</v>
-      </c>
-      <c r="V7">
-        <v>0.01553939635421855</v>
-      </c>
-      <c r="W7">
-        <v>0.160169336663215</v>
-      </c>
-      <c r="X7">
-        <v>0.08631795633844351</v>
-      </c>
-      <c r="Y7">
-        <v>0.07385138032477144</v>
-      </c>
-      <c r="Z7">
-        <v>0.08270449002308033</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.05745613080935483</v>
-      </c>
-      <c r="AC7">
-        <v>-0.05745613080935483</v>
-      </c>
-      <c r="AD7">
-        <v>8773.6</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>8773.6</v>
-      </c>
-      <c r="AG7">
-        <v>8695.6</v>
-      </c>
-      <c r="AH7">
-        <v>0.6360861590215398</v>
-      </c>
-      <c r="AI7">
-        <v>0.68458177278402</v>
-      </c>
-      <c r="AJ7">
-        <v>0.6340165219356767</v>
-      </c>
-      <c r="AK7">
-        <v>0.6826503375726174</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.095</v>
+        <v>0.08249999999999999</v>
       </c>
       <c r="E2">
-        <v>0.1405</v>
+        <v>0.1255</v>
       </c>
       <c r="F2">
-        <v>0.0455</v>
+        <v>0.0633</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,97 +603,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>-5.910304671947105E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>-4.687951248025226E-05</v>
       </c>
       <c r="K2">
-        <v>6808.5</v>
+        <v>7825.7</v>
       </c>
       <c r="L2">
-        <v>0.2981816111485805</v>
+        <v>0.3150303327952466</v>
       </c>
       <c r="M2">
-        <v>2326.558</v>
+        <v>2343.158</v>
       </c>
       <c r="N2">
-        <v>0.06206836019827232</v>
+        <v>0.05068402598273442</v>
       </c>
       <c r="O2">
-        <v>0.341713740177719</v>
+        <v>0.2994183267950471</v>
       </c>
       <c r="P2">
-        <v>2299.3</v>
+        <v>2315.9</v>
       </c>
       <c r="Q2">
-        <v>0.06134116605040044</v>
+        <v>0.05009441777866223</v>
       </c>
       <c r="R2">
-        <v>0.3377102151722112</v>
+        <v>0.2959351879065132</v>
       </c>
       <c r="S2">
         <v>27.25799999999995</v>
       </c>
       <c r="T2">
-        <v>0.01171601997457186</v>
+        <v>0.0116330183453271</v>
       </c>
       <c r="U2">
-        <v>51297</v>
+        <v>52696.8</v>
       </c>
       <c r="V2">
-        <v>1.368511196837034</v>
+        <v>1.139865933243494</v>
       </c>
       <c r="W2">
         <v>0.1228218896876897</v>
       </c>
       <c r="X2">
-        <v>0.1075489169108462</v>
+        <v>0.104052098082293</v>
       </c>
       <c r="Y2">
-        <v>0.0152729727768435</v>
+        <v>0.01876979160539671</v>
       </c>
       <c r="Z2">
-        <v>0.2535894838784196</v>
+        <v>0.2175792177871743</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.0607505882071487</v>
+        <v>0.06026097235856909</v>
       </c>
       <c r="AC2">
-        <v>-0.0607505882071487</v>
+        <v>-0.06037096307096958</v>
       </c>
       <c r="AD2">
-        <v>118409.6</v>
+        <v>138949.4</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>10.37092346931526</v>
       </c>
       <c r="AF2">
-        <v>118409.6</v>
+        <v>138959.7709234693</v>
       </c>
       <c r="AG2">
-        <v>67112.59999999999</v>
+        <v>86262.97092346931</v>
       </c>
       <c r="AH2">
-        <v>0.7595549266357652</v>
+        <v>0.7503613454328057</v>
       </c>
       <c r="AI2">
-        <v>0.6498042239337956</v>
+        <v>0.6598637823225892</v>
       </c>
       <c r="AJ2">
-        <v>0.641633937688104</v>
+        <v>0.651072389512827</v>
       </c>
       <c r="AK2">
-        <v>0.5125975260928841</v>
+        <v>0.5463424117605297</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>229289.4389438944</v>
+      </c>
+      <c r="AP2">
+        <v>142348.1368374081</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Erste Group Bank AG (WBAG:EBS)</t>
+          <t>BAWAG Group AG (WBAG:BG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.08199999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="E3">
-        <v>0.124</v>
+        <v>0.0907</v>
       </c>
       <c r="F3">
-        <v>0.068</v>
+        <v>0.0633</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,85 +740,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>3573.5</v>
+        <v>777</v>
       </c>
       <c r="L3">
-        <v>0.3000848147930436</v>
+        <v>0.4952830188679245</v>
       </c>
       <c r="M3">
-        <v>1349.6</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.05416751955625659</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.3776689520078355</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1322.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.05309187527342637</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.3701693018049531</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>26.79999999999995</v>
-      </c>
-      <c r="T3">
-        <v>0.01985773562537045</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>7317.6</v>
+        <v>1352.9</v>
       </c>
       <c r="V3">
-        <v>0.2936990523894956</v>
+        <v>0.2051153764516814</v>
       </c>
       <c r="W3">
-        <v>0.1606572854381154</v>
+        <v>0.1760467645459489</v>
       </c>
       <c r="X3">
-        <v>0.1049092666594396</v>
+        <v>0.1032256200746573</v>
       </c>
       <c r="Y3">
-        <v>0.05574801877867576</v>
+        <v>0.07282114447129154</v>
       </c>
       <c r="Z3">
-        <v>0.1661372118168184</v>
+        <v>0.0852673572989249</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0600226171939829</v>
+        <v>0.05913445613904493</v>
       </c>
       <c r="AC3">
-        <v>-0.0600226171939829</v>
+        <v>-0.05913445613904493</v>
       </c>
       <c r="AD3">
-        <v>68381.7</v>
+        <v>17353.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>68381.7</v>
+        <v>17353.3</v>
       </c>
       <c r="AG3">
-        <v>61064.1</v>
+        <v>16000.4</v>
       </c>
       <c r="AH3">
-        <v>0.7329463969902569</v>
+        <v>0.7245909032072186</v>
       </c>
       <c r="AI3">
-        <v>0.6706297368544932</v>
+        <v>0.7740408847812803</v>
       </c>
       <c r="AJ3">
-        <v>0.7102177963558713</v>
+        <v>0.708101362175941</v>
       </c>
       <c r="AK3">
-        <v>0.6451650734082208</v>
+        <v>0.7595294832480466</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -829,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Raiffeisen Bank International AG (WBAG:RBI)</t>
+          <t>Erste Group Bank AG (WBAG:EBS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,13 +841,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.12</v>
+        <v>0.08199999999999999</v>
       </c>
       <c r="E4">
-        <v>0.194</v>
+        <v>0.124</v>
       </c>
       <c r="F4">
-        <v>0.023</v>
+        <v>0.068</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +862,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2626.6</v>
+        <v>3573.5</v>
       </c>
       <c r="L4">
-        <v>0.2744446534177585</v>
+        <v>0.3000848147930436</v>
       </c>
       <c r="M4">
-        <v>872.2</v>
+        <v>1349.6</v>
       </c>
       <c r="N4">
-        <v>0.1298728371899104</v>
+        <v>0.05416751955625659</v>
       </c>
       <c r="O4">
-        <v>0.3320642655904972</v>
+        <v>0.3776689520078355</v>
       </c>
       <c r="P4">
-        <v>872.2</v>
+        <v>1322.8</v>
       </c>
       <c r="Q4">
-        <v>0.1298728371899104</v>
+        <v>0.05309187527342637</v>
       </c>
       <c r="R4">
-        <v>0.3320642655904972</v>
+        <v>0.3701693018049531</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>26.79999999999995</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.01985773562537045</v>
       </c>
       <c r="U4">
-        <v>43855.7</v>
+        <v>7317.6</v>
       </c>
       <c r="V4">
-        <v>6.530227225349176</v>
+        <v>0.2936990523894956</v>
       </c>
       <c r="W4">
-        <v>0.13342747998537</v>
+        <v>0.1606572854381154</v>
       </c>
       <c r="X4">
-        <v>0.1498315502968729</v>
+        <v>0.1048785760899286</v>
       </c>
       <c r="Y4">
-        <v>-0.01640407031150284</v>
+        <v>0.05577870934818677</v>
       </c>
       <c r="Z4">
-        <v>4.968384986762198</v>
+        <v>0.1661372118168184</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.06037845629967815</v>
+        <v>0.06001442116681656</v>
       </c>
       <c r="AC4">
-        <v>-0.06037845629967815</v>
+        <v>-0.06001442116681656</v>
       </c>
       <c r="AD4">
-        <v>39155.7</v>
+        <v>68381.7</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>39155.7</v>
+        <v>68381.7</v>
       </c>
       <c r="AG4">
-        <v>-4700</v>
+        <v>61064.1</v>
       </c>
       <c r="AH4">
-        <v>0.8535953696739805</v>
+        <v>0.7329463969902569</v>
       </c>
       <c r="AI4">
-        <v>0.624135463108045</v>
+        <v>0.6706297368544932</v>
       </c>
       <c r="AJ4">
-        <v>-2.331580513939875</v>
+        <v>0.7102177963558713</v>
       </c>
       <c r="AK4">
-        <v>-0.2489380409105836</v>
+        <v>0.6451650734082208</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oberbank AG (WBAG:OBS)</t>
+          <t>Raiffeisen Bank International AG (WBAG:RBI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +966,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0746</v>
+        <v>0.12</v>
       </c>
       <c r="E5">
-        <v>0.08699999999999999</v>
+        <v>0.194</v>
+      </c>
+      <c r="F5">
+        <v>0.023</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -981,28 +987,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>404.2</v>
+        <v>2626.6</v>
       </c>
       <c r="L5">
-        <v>0.4315148927084445</v>
+        <v>0.2744446534177585</v>
       </c>
       <c r="M5">
-        <v>82</v>
+        <v>872.2</v>
       </c>
       <c r="N5">
-        <v>0.01606960884220428</v>
+        <v>0.1298728371899104</v>
       </c>
       <c r="O5">
-        <v>0.2028698664027709</v>
+        <v>0.3320642655904972</v>
       </c>
       <c r="P5">
-        <v>82</v>
+        <v>872.2</v>
       </c>
       <c r="Q5">
-        <v>0.01606960884220428</v>
+        <v>0.1298728371899104</v>
       </c>
       <c r="R5">
-        <v>0.2028698664027709</v>
+        <v>0.3320642655904972</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1011,55 +1017,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>83</v>
+        <v>43855.7</v>
       </c>
       <c r="V5">
-        <v>0.01626557968174335</v>
+        <v>6.530227225349176</v>
       </c>
       <c r="W5">
-        <v>0.1002157042620187</v>
+        <v>0.13342747998537</v>
       </c>
       <c r="X5">
-        <v>0.0893243630570468</v>
+        <v>0.149777535288632</v>
       </c>
       <c r="Y5">
-        <v>0.01089134120497189</v>
+        <v>-0.01635005530326195</v>
       </c>
       <c r="Z5">
-        <v>0.07358844833410585</v>
+        <v>4.968384986762198</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.06112272011461925</v>
+        <v>0.0603705482523646</v>
       </c>
       <c r="AC5">
-        <v>-0.06112272011461925</v>
+        <v>-0.0603705482523646</v>
       </c>
       <c r="AD5">
-        <v>8542.1</v>
+        <v>39155.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>8542.1</v>
+        <v>39155.7</v>
       </c>
       <c r="AG5">
-        <v>8459.1</v>
+        <v>-4700</v>
       </c>
       <c r="AH5">
-        <v>0.6260287726549846</v>
+        <v>0.8535953696739805</v>
       </c>
       <c r="AI5">
-        <v>0.6532605287509273</v>
+        <v>0.624135463108045</v>
       </c>
       <c r="AJ5">
-        <v>0.6237400364255745</v>
+        <v>-2.331580513939875</v>
       </c>
       <c r="AK5">
-        <v>0.6510455549483957</v>
+        <v>-0.2489380409105836</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,117 +1082,367 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>Bank für Tirol und Vorarlberg AG (WBAG:BTS)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.083</v>
+      </c>
+      <c r="E6">
+        <v>0.127</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>-0.003345146260795289</v>
+      </c>
+      <c r="J6">
+        <v>-0.002872424582451089</v>
+      </c>
+      <c r="K6">
+        <v>240.2</v>
+      </c>
+      <c r="L6">
+        <v>0.5472772841193894</v>
+      </c>
+      <c r="M6">
+        <v>16.6</v>
+      </c>
+      <c r="N6">
+        <v>0.007716982009204594</v>
+      </c>
+      <c r="O6">
+        <v>0.06910907577019151</v>
+      </c>
+      <c r="P6">
+        <v>16.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.007716982009204594</v>
+      </c>
+      <c r="R6">
+        <v>0.06910907577019151</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>46.9</v>
+      </c>
+      <c r="V6">
+        <v>0.02180279856817442</v>
+      </c>
+      <c r="W6">
+        <v>0.103334050333405</v>
+      </c>
+      <c r="X6">
+        <v>0.08656858454146396</v>
+      </c>
+      <c r="Y6">
+        <v>0.01676546579194106</v>
+      </c>
+      <c r="Z6">
+        <v>0.07658388183451233</v>
+      </c>
+      <c r="AA6">
+        <v>-0.0002199814248009826</v>
+      </c>
+      <c r="AB6">
+        <v>0.06015139646477358</v>
+      </c>
+      <c r="AC6">
+        <v>-0.06037137788957456</v>
+      </c>
+      <c r="AD6">
+        <v>3186.5</v>
+      </c>
+      <c r="AE6">
+        <v>10.37092346931526</v>
+      </c>
+      <c r="AF6">
+        <v>3196.870923469315</v>
+      </c>
+      <c r="AG6">
+        <v>3149.970923469315</v>
+      </c>
+      <c r="AH6">
+        <v>0.5977726822410346</v>
+      </c>
+      <c r="AI6">
+        <v>0.5376533058463102</v>
+      </c>
+      <c r="AJ6">
+        <v>0.5942140689956661</v>
+      </c>
+      <c r="AK6">
+        <v>0.5339774626097865</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>5258.250825082509</v>
+      </c>
+      <c r="AP6">
+        <v>5197.97182090646</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Oberbank AG (WBAG:OBS)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.0746</v>
+      </c>
+      <c r="E7">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>404.2</v>
+      </c>
+      <c r="L7">
+        <v>0.4315148927084445</v>
+      </c>
+      <c r="M7">
+        <v>82</v>
+      </c>
+      <c r="N7">
+        <v>0.01606960884220428</v>
+      </c>
+      <c r="O7">
+        <v>0.2028698664027709</v>
+      </c>
+      <c r="P7">
+        <v>82</v>
+      </c>
+      <c r="Q7">
+        <v>0.01606960884220428</v>
+      </c>
+      <c r="R7">
+        <v>0.2028698664027709</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>83</v>
+      </c>
+      <c r="V7">
+        <v>0.01626557968174335</v>
+      </c>
+      <c r="W7">
+        <v>0.1002157042620187</v>
+      </c>
+      <c r="X7">
+        <v>0.08930176444323688</v>
+      </c>
+      <c r="Y7">
+        <v>0.0109139398187818</v>
+      </c>
+      <c r="Z7">
+        <v>0.07358844833410585</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0.06111426888327647</v>
+      </c>
+      <c r="AC7">
+        <v>-0.06111426888327647</v>
+      </c>
+      <c r="AD7">
+        <v>8542.1</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>8542.1</v>
+      </c>
+      <c r="AG7">
+        <v>8459.1</v>
+      </c>
+      <c r="AH7">
+        <v>0.6260287726549846</v>
+      </c>
+      <c r="AI7">
+        <v>0.6532605287509273</v>
+      </c>
+      <c r="AJ7">
+        <v>0.6237400364255745</v>
+      </c>
+      <c r="AK7">
+        <v>0.6510455549483957</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>BKS Bank AG (WBAG:BKS)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="D8">
         <v>0.108</v>
       </c>
-      <c r="E6">
+      <c r="E8">
         <v>0.157</v>
       </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
         <v>204.2</v>
       </c>
-      <c r="L6">
+      <c r="L8">
         <v>0.488750598372427</v>
       </c>
-      <c r="M6">
+      <c r="M8">
         <v>22.758</v>
       </c>
-      <c r="N6">
+      <c r="N8">
         <v>0.03034804640618749</v>
       </c>
-      <c r="O6">
+      <c r="O8">
         <v>0.1114495592556317</v>
       </c>
-      <c r="P6">
+      <c r="P8">
         <v>22.3</v>
       </c>
-      <c r="Q6">
+      <c r="Q8">
         <v>0.02973729830644086</v>
       </c>
-      <c r="R6">
+      <c r="R8">
         <v>0.1092066601371205</v>
       </c>
-      <c r="S6">
+      <c r="S8">
         <v>0.4579999999999984</v>
       </c>
-      <c r="T6">
+      <c r="T8">
         <v>0.02012479128218642</v>
       </c>
-      <c r="U6">
+      <c r="U8">
         <v>40.7</v>
       </c>
-      <c r="V6">
+      <c r="V8">
         <v>0.05427390318709162</v>
       </c>
-      <c r="W6">
+      <c r="W8">
         <v>0.1122162993900093</v>
       </c>
-      <c r="X6">
-        <v>0.1101885671622528</v>
-      </c>
-      <c r="Y6">
-        <v>0.002027732227756582</v>
-      </c>
-      <c r="Z6">
+      <c r="X8">
+        <v>0.1101551354871891</v>
+      </c>
+      <c r="Y8">
+        <v>0.002061163902820198</v>
+      </c>
+      <c r="Z8">
         <v>0.1126722580297187</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.06153132713016055</v>
-      </c>
-      <c r="AC6">
-        <v>-0.06153132713016055</v>
-      </c>
-      <c r="AD6">
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0.06152318738563775</v>
+      </c>
+      <c r="AC8">
+        <v>-0.06152318738563775</v>
+      </c>
+      <c r="AD8">
         <v>2330.1</v>
       </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
         <v>2330.1</v>
       </c>
-      <c r="AG6">
+      <c r="AG8">
         <v>2289.4</v>
       </c>
-      <c r="AH6">
+      <c r="AH8">
         <v>0.756525974025974</v>
       </c>
-      <c r="AI6">
+      <c r="AI8">
         <v>0.5241951812107714</v>
       </c>
-      <c r="AJ6">
+      <c r="AJ8">
         <v>0.7532655545684861</v>
       </c>
-      <c r="AK6">
+      <c r="AK8">
         <v>0.5197983834347472</v>
       </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
         <v>0</v>
       </c>
     </row>
